--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -2676,10 +2676,10 @@
         <v>0.0001072884629139547</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0001072884629139546</v>
+        <v>0.0001072884629139547</v>
       </c>
       <c r="D63" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738252e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C76" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
         <v>0.0001072884629139547</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0001072884629139546</v>
+        <v>0.0001072884629139547</v>
       </c>
       <c r="D162" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C173" t="n">
-        <v>3.814343201886829e-05</v>
+        <v>3.814343201886828e-05</v>
       </c>
       <c r="D173" t="n">
-        <v>5.085790935849099e-06</v>
+        <v>5.085790935849106e-06</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738252e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D182" t="n">
-        <v>1.461514665081737e-06</v>
+        <v>1.461514665081733e-06</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D196" t="n">
-        <v>9.093652217404419e-06</v>
+        <v>9.093652217404422e-06</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>2.859692749844802e-05</v>
       </c>
       <c r="D210" t="n">
-        <v>3.872500598748167e-06</v>
+        <v>3.87250059874817e-06</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8008,10 +8008,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C226" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8104,10 +8104,10 @@
         <v>0.0003836945177727301</v>
       </c>
       <c r="C229" t="n">
-        <v>0.00038369451777273</v>
+        <v>0.0003836945177727301</v>
       </c>
       <c r="D229" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -8520,10 +8520,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0002766307721372088</v>
+        <v>0.0002766307721372089</v>
       </c>
       <c r="D242" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8715,7 +8715,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>9.882286761156534e-05</v>
+        <v>9.882286761156532e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>8.062279496655769e-05</v>
+        <v>8.062279496655767e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -9192,10 +9192,10 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>6.449823597324612e-05</v>
+        <v>6.449823597324613e-05</v>
       </c>
       <c r="D263" t="n">
-        <v>1.289964719464938e-06</v>
+        <v>1.289964719464924e-06</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0009141696292534283</v>
+        <v>0.0009141696292534281</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9608,10 +9608,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C276" t="n">
-        <v>0.0001298000041536002</v>
+        <v>0.0001298000041536001</v>
       </c>
       <c r="D276" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.50753524550316e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9800,10 +9800,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9928,10 +9928,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C286" t="n">
-        <v>6.295184515171394e-05</v>
+        <v>6.295184515171395e-05</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10952,10 +10952,10 @@
         <v>0.0001072884629139547</v>
       </c>
       <c r="C318" t="n">
-        <v>0.0001072884629139546</v>
+        <v>0.0001072884629139547</v>
       </c>
       <c r="D318" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738252e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11368,10 +11368,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C331" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13652,10 +13652,10 @@
         <v>0.0003836945177727301</v>
       </c>
       <c r="C403" t="n">
-        <v>0.00038369451777273</v>
+        <v>0.0003836945177727301</v>
       </c>
       <c r="D403" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002766307721372088</v>
+        <v>0.0002766307721372089</v>
       </c>
       <c r="D428" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14607,7 +14607,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>9.882286761156534e-05</v>
+        <v>9.882286761156532e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.2765871227126e-06</v>
+        <v>2.276587122712603e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>8.062279496655769e-05</v>
+        <v>8.062279496655767e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582752e-06</v>
+        <v>2.991280417582749e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15388,10 +15388,10 @@
         <v>3.459325613575122e-05</v>
       </c>
       <c r="C465" t="n">
-        <v>3.095186075304057e-05</v>
+        <v>3.095186075304056e-05</v>
       </c>
       <c r="D465" t="n">
-        <v>3.64139538271065e-06</v>
+        <v>3.641395382710656e-06</v>
       </c>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
@@ -15528,10 +15528,10 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>6.449823597324612e-05</v>
+        <v>6.449823597324613e-05</v>
       </c>
       <c r="D470" t="n">
-        <v>1.289964719464938e-06</v>
+        <v>1.289964719464924e-06</v>
       </c>
       <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0009141696292534283</v>
+        <v>0.0009141696292534281</v>
       </c>
       <c r="D547" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961826e-05</v>
+        <v>5.528672749961824e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752819e-06</v>
+        <v>1.316350654752832e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -17992,10 +17992,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C558" t="n">
-        <v>0.0001298000041536002</v>
+        <v>0.0001298000041536001</v>
       </c>
       <c r="D558" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.50753524550316e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18244,10 +18244,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C567" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D567" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D568" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18524,10 +18524,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C577" t="n">
-        <v>6.295184515171394e-05</v>
+        <v>6.295184515171395e-05</v>
       </c>
       <c r="D577" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr"/>
@@ -18860,10 +18860,10 @@
         <v>3.872023028148663e-05</v>
       </c>
       <c r="C589" t="n">
-        <v>3.683143856043849e-05</v>
+        <v>3.68314385604385e-05</v>
       </c>
       <c r="D589" t="n">
-        <v>1.888791721048136e-06</v>
+        <v>1.88879172104813e-06</v>
       </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21520,10 +21520,10 @@
         <v>0.0001072884629139547</v>
       </c>
       <c r="C684" t="n">
-        <v>0.0001072884629139546</v>
+        <v>0.0001072884629139547</v>
       </c>
       <c r="D684" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21828,10 +21828,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C695" t="n">
-        <v>3.814343201886829e-05</v>
+        <v>3.814343201886828e-05</v>
       </c>
       <c r="D695" t="n">
-        <v>5.085790935849099e-06</v>
+        <v>5.085790935849106e-06</v>
       </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738252e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22083,7 +22083,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D704" t="n">
-        <v>1.461514665081737e-06</v>
+        <v>1.461514665081733e-06</v>
       </c>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D718" t="n">
-        <v>9.093652217404419e-06</v>
+        <v>9.093652217404422e-06</v>
       </c>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
         <v>2.859692749844802e-05</v>
       </c>
       <c r="D732" t="n">
-        <v>3.872500598748167e-06</v>
+        <v>3.87250059874817e-06</v>
       </c>
       <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D747" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23312,10 +23312,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C748" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -480,10 +480,10 @@
         <v>0.0004249893752656184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000445889471595908</v>
+        <v>0.0004249893752656183</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.090009633028969e-05</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -516,10 +516,10 @@
         <v>0.0002690341673392521</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002736077828201949</v>
+        <v>0.000269034167339252</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.573615480942862e-06</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -552,10 +552,10 @@
         <v>0.0001252114110578495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001241630074981866</v>
+        <v>0.0001233425840271354</v>
       </c>
       <c r="D4" t="n">
-        <v>1.048403559662976e-06</v>
+        <v>1.868827030714152e-06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>0.005405405405405406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005707350427350428</v>
+        <v>0.005405405405405406</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0003019450219450227</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>0.003996003996003996</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004265447138750306</v>
+        <v>0.003996003996003996</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0002694431427463099</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         <v>0.0008048289738430583</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009068495479921784</v>
+        <v>0.0008048289738430583</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00010202057414912</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>0.0003755692221022487</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003813358449739002</v>
+        <v>0.0003755692221022487</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.766622871651431e-06</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -732,10 +732,10 @@
         <v>9.69976831864852e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.772759287638872e-05</v>
+        <v>9.699768318648521e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.299096899035236e-07</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
         <v>0.0001527628979121734</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001540328862940533</v>
+        <v>0.0001527628979121734</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.269988381879898e-06</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>0.02795248078266946</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02892742831014436</v>
+        <v>0.02795248078266947</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0009749475274748974</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         <v>0.004048582995951417</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004733727810650887</v>
+        <v>0.004048582995951417</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0006851448146994697</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -876,10 +876,10 @@
         <v>0.006451612903225806</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007688750144525377</v>
+        <v>0.006451612903225806</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.001237137241299571</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>0.1396825396825397</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1430003277726983</v>
+        <v>0.1396825396825397</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.003317788090158591</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         <v>0.1756214915797915</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1773198264280309</v>
+        <v>0.1756214915797915</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.001698334848239419</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         <v>0.1184210526315789</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1220799419041607</v>
+        <v>0.1184210526315789</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00365888927258172</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>0.0003320880033208801</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0003380241065164837</v>
+        <v>0.00033208800332088</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.936103195603598e-06</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         <v>0.0002788551727634547</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0002841051163853209</v>
+        <v>0.0002788551727634547</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.249943621866114e-06</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>8.177577330764418e-05</v>
       </c>
       <c r="C19" t="n">
-        <v>8.222078520048327e-05</v>
+        <v>8.177577330764418e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.450118928390898e-07</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         <v>5.677872792631042e-05</v>
       </c>
       <c r="C20" t="n">
-        <v>5.622435835598398e-05</v>
+        <v>5.601144781919812e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>5.543695703264377e-07</v>
+        <v>7.672801071122973e-07</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>4.816666614025502e-05</v>
       </c>
       <c r="C21" t="n">
-        <v>4.83384640280829e-05</v>
+        <v>4.816666614025501e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.717978878278793e-07</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>4.221507380305824e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>4.232014284597981e-05</v>
+        <v>4.221507380305824e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.050690429215737e-07</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>0.306184012066365</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3148696033311418</v>
+        <v>0.306184012066365</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.008685591264776749</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>0.6994482310938007</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7004600911026164</v>
+        <v>0.6994482310938007</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.001011860008815701</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>0.09090909090909091</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09367252066115704</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.002763429752066129</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         <v>9.995502024089161e-05</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0001012559254221113</v>
+        <v>9.995502024089161e-05</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.30090518121967e-06</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         <v>4.877771833826308e-05</v>
       </c>
       <c r="C27" t="n">
-        <v>4.900129517370613e-05</v>
+        <v>4.877771833826308e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.235768354430463e-07</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
         <v>0.0001522986715402242</v>
       </c>
       <c r="C28" t="n">
-        <v>0.000154434143758464</v>
+        <v>0.0001522986715402242</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.135472218239886e-06</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684897</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.138833436738252e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D112" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684897</v>
       </c>
       <c r="D161" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>2.998886128009596e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027425e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>7.138833436738252e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D181" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>3.064100992768722e-05</v>
+        <v>3.064100992768721e-05</v>
       </c>
       <c r="D183" t="n">
-        <v>3.953678700346738e-06</v>
+        <v>3.953678700346745e-06</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D209" t="n">
-        <v>4.404238639266429e-06</v>
+        <v>4.404238639266433e-06</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D225" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8104,10 +8104,10 @@
         <v>0.0003836945177727301</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0003836945177727301</v>
+        <v>0.00038369451777273</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>8.062279496655767e-05</v>
+        <v>8.062279496655766e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8939,7 +8939,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8971,7 +8971,7 @@
         <v>0.0003117345802716544</v>
       </c>
       <c r="D256" t="n">
-        <v>9.681198145082039e-07</v>
+        <v>9.681198145082581e-07</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9128,10 +9128,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D261" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9224,10 +9224,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C264" t="n">
-        <v>4.458369214044474e-05</v>
+        <v>4.458369214044473e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.221471017546425e-06</v>
+        <v>1.221471017546432e-06</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9291,7 +9291,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0009141696292534281</v>
+        <v>0.0009141696292534282</v>
       </c>
       <c r="D271" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.000734172278113636</v>
+        <v>0.0007341722781136362</v>
       </c>
       <c r="D272" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D277" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.50753524550316e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9800,10 +9800,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C282" t="n">
-        <v>0.000155559703814324</v>
+        <v>0.0001555597038143239</v>
       </c>
       <c r="D282" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9864,10 +9864,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D284" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>0.0001776279832392057</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>5.130361861523299e-05</v>
+        <v>5.130361861523298e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684897</v>
       </c>
       <c r="D317" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C319" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>7.138833436738252e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D325" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D330" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11435,7 +11435,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13652,10 +13652,10 @@
         <v>0.0003836945177727301</v>
       </c>
       <c r="C403" t="n">
-        <v>0.0003836945177727301</v>
+        <v>0.00038369451777273</v>
       </c>
       <c r="D403" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D429" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14688,10 +14688,10 @@
         <v>2.991280417582746e-05</v>
       </c>
       <c r="C440" t="n">
-        <v>2.542588354945334e-05</v>
+        <v>2.542588354945335e-05</v>
       </c>
       <c r="D440" t="n">
-        <v>4.486920626374119e-06</v>
+        <v>4.486920626374116e-06</v>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>8.062279496655767e-05</v>
+        <v>8.062279496655766e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -15055,7 +15055,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D453" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15083,7 +15083,7 @@
         <v>0.0003117345802716544</v>
       </c>
       <c r="D454" t="n">
-        <v>9.681198145082039e-07</v>
+        <v>9.681198145082581e-07</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D462" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C471" t="n">
-        <v>4.458369214044474e-05</v>
+        <v>4.458369214044473e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.221471017546425e-06</v>
+        <v>1.221471017546432e-06</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -15643,7 +15643,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17463,7 +17463,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D539" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0009141696292534281</v>
+        <v>0.0009141696292534282</v>
       </c>
       <c r="D547" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.000734172278113636</v>
+        <v>0.0007341722781136362</v>
       </c>
       <c r="D548" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961824e-05</v>
+        <v>5.528672749961825e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752832e-06</v>
+        <v>1.316350654752826e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D559" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.50753524550316e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18244,10 +18244,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C567" t="n">
-        <v>0.000155559703814324</v>
+        <v>0.0001555597038143239</v>
       </c>
       <c r="D567" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18468,10 +18468,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D575" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr"/>
@@ -18723,7 +18723,7 @@
         <v>0.0001776279832392057</v>
       </c>
       <c r="D584" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18807,7 +18807,7 @@
         <v>2.91604881589805e-05</v>
       </c>
       <c r="D587" t="n">
-        <v>3.722615509657083e-06</v>
+        <v>3.72261550965708e-06</v>
       </c>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>5.130361861523299e-05</v>
+        <v>5.130361861523298e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684897</v>
       </c>
       <c r="D683" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>2.998886128009596e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027425e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21716,10 +21716,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C691" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>7.138833436738252e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D703" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C705" t="n">
-        <v>3.064100992768722e-05</v>
+        <v>3.064100992768721e-05</v>
       </c>
       <c r="D705" t="n">
-        <v>3.953678700346738e-06</v>
+        <v>3.953678700346745e-06</v>
       </c>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22839,7 +22839,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D731" t="n">
-        <v>4.404238639266429e-06</v>
+        <v>4.404238639266433e-06</v>
       </c>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D747" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23340,10 +23340,10 @@
         <v>6.743891993347184e-06</v>
       </c>
       <c r="C749" t="n">
-        <v>6.702706149360693e-06</v>
+        <v>6.702339406836483e-06</v>
       </c>
       <c r="D749" t="n">
-        <v>4.118584398649112e-08</v>
+        <v>4.155258651070105e-08</v>
       </c>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr"/>
@@ -23368,10 +23368,10 @@
         <v>8.941126120184445e-06</v>
       </c>
       <c r="C750" t="n">
-        <v>8.889013740048229e-06</v>
+        <v>8.888335803639654e-06</v>
       </c>
       <c r="D750" t="n">
-        <v>5.211238013621678e-08</v>
+        <v>5.279031654479102e-08</v>
       </c>
       <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D30" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684897</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D62" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>5.042128030135118e-05</v>
+        <v>5.042128030135119e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D74" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>5.561865052818271e-05</v>
+        <v>5.561865052818272e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D93" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684897</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D161" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C165" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027425e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C173" t="n">
-        <v>3.814343201886828e-05</v>
+        <v>3.814343201886829e-05</v>
       </c>
       <c r="D173" t="n">
-        <v>5.085790935849106e-06</v>
+        <v>5.085790935849099e-06</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D179" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D182" t="n">
-        <v>1.461514665081733e-06</v>
+        <v>1.461514665081737e-06</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>3.064100992768721e-05</v>
+        <v>3.064100992768722e-05</v>
       </c>
       <c r="D183" t="n">
-        <v>3.953678700346745e-06</v>
+        <v>3.953678700346738e-06</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>5.042128030135118e-05</v>
+        <v>5.042128030135119e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>5.561865052818271e-05</v>
+        <v>5.561865052818272e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D197" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218099e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D198" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7499,7 +7499,7 @@
         <v>2.859692749844802e-05</v>
       </c>
       <c r="D210" t="n">
-        <v>3.87250059874817e-06</v>
+        <v>3.872500598748167e-06</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D224" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8075,7 +8075,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D228" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D230" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D231" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8395,7 +8395,7 @@
         <v>0.0001027010372804765</v>
       </c>
       <c r="D238" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -8520,10 +8520,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0002766307721372089</v>
+        <v>0.0002766307721372088</v>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D243" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8715,7 +8715,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D248" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8747,7 +8747,7 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8939,7 +8939,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D255" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0003117345802716544</v>
+        <v>0.0003117345802716545</v>
       </c>
       <c r="D256" t="n">
-        <v>9.681198145082581e-07</v>
+        <v>9.681198145081497e-07</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9096,10 +9096,10 @@
         <v>0.0001449275362318841</v>
       </c>
       <c r="C260" t="n">
-        <v>0.0001405357927097057</v>
+        <v>0.0001405357927097058</v>
       </c>
       <c r="D260" t="n">
-        <v>4.391743522178307e-06</v>
+        <v>4.39174352217828e-06</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9163,7 +9163,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D262" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9256,10 +9256,10 @@
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C265" t="n">
-        <v>6.105992852396602e-05</v>
+        <v>6.105992852396603e-05</v>
       </c>
       <c r="D265" t="n">
-        <v>1.795880250704879e-06</v>
+        <v>1.795880250704865e-06</v>
       </c>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0007341722781136362</v>
+        <v>0.0007341722781136361</v>
       </c>
       <c r="D272" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9544,10 +9544,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C274" t="n">
-        <v>7.458734551096062e-05</v>
+        <v>7.458734551096063e-05</v>
       </c>
       <c r="D274" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9576,10 +9576,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C275" t="n">
-        <v>6.709560770963845e-05</v>
+        <v>6.709560770963846e-05</v>
       </c>
       <c r="D275" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9800,10 +9800,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9896,10 +9896,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C285" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -9928,10 +9928,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C286" t="n">
-        <v>6.295184515171395e-05</v>
+        <v>6.295184515171397e-05</v>
       </c>
       <c r="D286" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -10059,7 +10059,7 @@
         <v>0.0001776279832392057</v>
       </c>
       <c r="D290" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10152,10 +10152,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C293" t="n">
-        <v>6.822724220135866e-05</v>
+        <v>6.822724220135864e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>5.130361861523298e-05</v>
+        <v>5.130361861523299e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684897</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D317" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11115,7 +11115,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D323" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11208,10 +11208,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C326" t="n">
-        <v>5.042128030135118e-05</v>
+        <v>5.042128030135119e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11240,10 +11240,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D329" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>5.561865052818271e-05</v>
+        <v>5.561865052818272e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13543,7 +13543,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D399" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13683,7 +13683,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D404" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D405" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         <v>1.725661273399967e-05</v>
       </c>
       <c r="C416" t="n">
-        <v>1.380529018719973e-05</v>
+        <v>1.380529018719974e-05</v>
       </c>
       <c r="D416" t="n">
-        <v>3.451322546799936e-06</v>
+        <v>3.451322546799934e-06</v>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
@@ -14159,7 +14159,7 @@
         <v>0.0001027010372804765</v>
       </c>
       <c r="D421" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002766307721372089</v>
+        <v>0.0002766307721372088</v>
       </c>
       <c r="D428" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D429" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14607,7 +14607,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D437" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14635,7 +14635,7 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="D438" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14688,10 +14688,10 @@
         <v>2.991280417582746e-05</v>
       </c>
       <c r="C440" t="n">
-        <v>2.542588354945335e-05</v>
+        <v>2.542588354945334e-05</v>
       </c>
       <c r="D440" t="n">
-        <v>4.486920626374116e-06</v>
+        <v>4.486920626374123e-06</v>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.276587122712603e-06</v>
+        <v>2.2765871227126e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15055,7 +15055,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D453" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0003117345802716544</v>
+        <v>0.0003117345802716545</v>
       </c>
       <c r="D454" t="n">
-        <v>9.681198145082581e-07</v>
+        <v>9.681198145081497e-07</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15276,10 +15276,10 @@
         <v>0.0001449275362318841</v>
       </c>
       <c r="C461" t="n">
-        <v>0.0001405357927097057</v>
+        <v>0.0001405357927097058</v>
       </c>
       <c r="D461" t="n">
-        <v>4.391743522178307e-06</v>
+        <v>4.39174352217828e-06</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15335,7 +15335,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D463" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582749e-06</v>
+        <v>2.991280417582752e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15584,10 +15584,10 @@
         <v>6.28558087746709e-05</v>
       </c>
       <c r="C472" t="n">
-        <v>6.105992852396602e-05</v>
+        <v>6.105992852396603e-05</v>
       </c>
       <c r="D472" t="n">
-        <v>1.795880250704879e-06</v>
+        <v>1.795880250704865e-06</v>
       </c>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0007341722781136362</v>
+        <v>0.0007341722781136361</v>
       </c>
       <c r="D548" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17768,10 +17768,10 @@
         <v>4.151028244288012e-05</v>
       </c>
       <c r="C550" t="n">
-        <v>3.978068734109345e-05</v>
+        <v>3.978068734109346e-05</v>
       </c>
       <c r="D550" t="n">
-        <v>1.729595101786666e-06</v>
+        <v>1.729595101786659e-06</v>
       </c>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961825e-05</v>
+        <v>5.528672749961826e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752826e-06</v>
+        <v>1.316350654752819e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -17936,10 +17936,10 @@
         <v>7.45873455109606e-05</v>
       </c>
       <c r="C556" t="n">
-        <v>7.458734551096062e-05</v>
+        <v>7.458734551096063e-05</v>
       </c>
       <c r="D556" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C557" t="n">
-        <v>6.709560770963845e-05</v>
+        <v>6.709560770963846e-05</v>
       </c>
       <c r="D557" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D559" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18244,10 +18244,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C567" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D567" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18496,10 +18496,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C576" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D576" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr"/>
@@ -18524,10 +18524,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C577" t="n">
-        <v>6.295184515171395e-05</v>
+        <v>6.295184515171397e-05</v>
       </c>
       <c r="D577" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr"/>
@@ -18723,7 +18723,7 @@
         <v>0.0001776279832392057</v>
       </c>
       <c r="D584" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18804,10 +18804,10 @@
         <v>3.288310366863758e-05</v>
       </c>
       <c r="C587" t="n">
-        <v>2.91604881589805e-05</v>
+        <v>2.916048815898051e-05</v>
       </c>
       <c r="D587" t="n">
-        <v>3.72261550965708e-06</v>
+        <v>3.722615509657076e-06</v>
       </c>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr"/>
@@ -18972,10 +18972,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C593" t="n">
-        <v>6.822724220135866e-05</v>
+        <v>6.822724220135864e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>5.130361861523298e-05</v>
+        <v>5.130361861523299e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684897</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D683" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C687" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027425e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>0</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21828,10 +21828,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C695" t="n">
-        <v>3.814343201886828e-05</v>
+        <v>3.814343201886829e-05</v>
       </c>
       <c r="D695" t="n">
-        <v>5.085790935849106e-06</v>
+        <v>5.085790935849099e-06</v>
       </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D701" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D703" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22083,7 +22083,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D704" t="n">
-        <v>1.461514665081733e-06</v>
+        <v>1.461514665081737e-06</v>
       </c>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C705" t="n">
-        <v>3.064100992768721e-05</v>
+        <v>3.064100992768722e-05</v>
       </c>
       <c r="D705" t="n">
-        <v>3.953678700346745e-06</v>
+        <v>3.953678700346738e-06</v>
       </c>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr"/>
@@ -22248,10 +22248,10 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="C710" t="n">
-        <v>5.042128030135118e-05</v>
+        <v>5.042128030135119e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22276,10 +22276,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>5.561865052818271e-05</v>
+        <v>5.561865052818272e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22503,7 +22503,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D719" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218099e-06</v>
       </c>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr"/>
@@ -22531,7 +22531,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D720" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -22867,7 +22867,7 @@
         <v>2.859692749844802e-05</v>
       </c>
       <c r="D732" t="n">
-        <v>3.87250059874817e-06</v>
+        <v>3.872500598748167e-06</v>
       </c>
       <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D746" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -23333,7 +23333,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -23361,7 +23361,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B750" t="n">

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D30" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D35" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.138833436738255e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C76" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D93" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D105" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D107" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D112" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D161" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>2.998886128009596e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027425e-06</v>
+        <v>8.568246080027422e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>7.138833436738255e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D182" t="n">
-        <v>1.461514665081733e-06</v>
+        <v>1.461514665081737e-06</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D196" t="n">
-        <v>9.093652217404422e-06</v>
+        <v>9.093652217404419e-06</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D197" t="n">
-        <v>3.131201246218099e-06</v>
+        <v>3.131201246218096e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D198" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7307,7 +7307,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D204" t="n">
-        <v>4.367602868959209e-06</v>
+        <v>4.367602868959212e-06</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         <v>3.246942809719619e-05</v>
       </c>
       <c r="C210" t="n">
-        <v>2.859692749844803e-05</v>
+        <v>2.859692749844802e-05</v>
       </c>
       <c r="D210" t="n">
-        <v>3.872500598748163e-06</v>
+        <v>3.872500598748167e-06</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -8008,10 +8008,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C226" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8075,7 +8075,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D228" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D230" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D231" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8395,7 +8395,7 @@
         <v>0.0001027010372804765</v>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -8424,10 +8424,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>6.598963615398507e-05</v>
+        <v>6.598963615398509e-05</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8715,7 +8715,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8747,7 +8747,7 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="D249" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8776,10 +8776,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C250" t="n">
-        <v>9.882286761156532e-05</v>
+        <v>9.882286761156534e-05</v>
       </c>
       <c r="D250" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>8.062279496655769e-05</v>
+        <v>8.062279496655766e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8939,7 +8939,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D255" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9163,7 +9163,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D262" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9291,7 +9291,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D266" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0007341722781136361</v>
+        <v>0.000734172278113636</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D277" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D283" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9864,10 +9864,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D284" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9896,10 +9896,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C285" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D317" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>7.138833436738255e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11368,10 +11368,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C331" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -11435,7 +11435,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D333" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>0</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13543,7 +13543,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D399" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13683,7 +13683,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D404" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D405" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         <v>1.725661273399967e-05</v>
       </c>
       <c r="C416" t="n">
-        <v>1.380529018719974e-05</v>
+        <v>1.380529018719973e-05</v>
       </c>
       <c r="D416" t="n">
-        <v>3.451322546799934e-06</v>
+        <v>3.451322546799936e-06</v>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
@@ -14159,7 +14159,7 @@
         <v>0.0001027010372804765</v>
       </c>
       <c r="D421" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>6.598963615398507e-05</v>
+        <v>6.598963615398509e-05</v>
       </c>
       <c r="D422" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14607,7 +14607,7 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14635,7 +14635,7 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="D438" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14660,10 +14660,10 @@
         <v>9.882286761156531e-05</v>
       </c>
       <c r="C439" t="n">
-        <v>9.882286761156532e-05</v>
+        <v>9.882286761156534e-05</v>
       </c>
       <c r="D439" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
         <v>2.542588354945334e-05</v>
       </c>
       <c r="D440" t="n">
-        <v>4.486920626374123e-06</v>
+        <v>4.486920626374119e-06</v>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.2765871227126e-06</v>
+        <v>2.276587122712603e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>8.062279496655769e-05</v>
+        <v>8.062279496655766e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15055,7 +15055,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D453" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15335,7 +15335,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D463" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582752e-06</v>
+        <v>2.991280417582749e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15643,7 +15643,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D474" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17463,7 +17463,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D539" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.0007341722781136361</v>
+        <v>0.000734172278113636</v>
       </c>
       <c r="D548" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17768,10 +17768,10 @@
         <v>4.151028244288012e-05</v>
       </c>
       <c r="C550" t="n">
-        <v>3.978068734109346e-05</v>
+        <v>3.978068734109345e-05</v>
       </c>
       <c r="D550" t="n">
-        <v>1.729595101786659e-06</v>
+        <v>1.729595101786666e-06</v>
       </c>
       <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr"/>
@@ -17796,10 +17796,10 @@
         <v>4.386457426798799e-05</v>
       </c>
       <c r="C551" t="n">
-        <v>4.210999129726847e-05</v>
+        <v>4.210999129726846e-05</v>
       </c>
       <c r="D551" t="n">
-        <v>1.75458297071952e-06</v>
+        <v>1.754582970719526e-06</v>
       </c>
       <c r="E551" t="inlineStr"/>
       <c r="F551" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961826e-05</v>
+        <v>5.528672749961825e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752819e-06</v>
+        <v>1.316350654752826e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D559" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D568" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18468,10 +18468,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D575" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr"/>
@@ -18496,10 +18496,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C576" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D576" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D683" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21607,7 +21607,7 @@
         <v>2.998886128009596e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027425e-06</v>
+        <v>8.568246080027422e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>7.138833436738255e-05</v>
+        <v>7.138833436738254e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D703" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22083,7 +22083,7 @@
         <v>2.48457493063895e-05</v>
       </c>
       <c r="D704" t="n">
-        <v>1.461514665081733e-06</v>
+        <v>1.461514665081737e-06</v>
       </c>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D718" t="n">
-        <v>9.093652217404422e-06</v>
+        <v>9.093652217404419e-06</v>
       </c>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr"/>
@@ -22503,7 +22503,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D719" t="n">
-        <v>3.131201246218099e-06</v>
+        <v>3.131201246218096e-06</v>
       </c>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr"/>
@@ -22531,7 +22531,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D720" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -22699,7 +22699,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D726" t="n">
-        <v>4.367602868959209e-06</v>
+        <v>4.367602868959212e-06</v>
       </c>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr"/>
@@ -22864,10 +22864,10 @@
         <v>3.246942809719619e-05</v>
       </c>
       <c r="C732" t="n">
-        <v>2.859692749844803e-05</v>
+        <v>2.859692749844802e-05</v>
       </c>
       <c r="D732" t="n">
-        <v>3.872500598748163e-06</v>
+        <v>3.872500598748167e-06</v>
       </c>
       <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr"/>
@@ -23312,10 +23312,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C748" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D30" t="n">
-        <v>5.308700960874859e-06</v>
+        <v>5.308700960874886e-06</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D70" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C76" t="n">
-        <v>5.522161491500571e-05</v>
+        <v>5.522161491500572e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D93" t="n">
-        <v>5.308700960874859e-06</v>
+        <v>5.308700960874886e-06</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C173" t="n">
-        <v>3.814343201886828e-05</v>
+        <v>3.814343201886829e-05</v>
       </c>
       <c r="D173" t="n">
-        <v>5.085790935849106e-06</v>
+        <v>5.085790935849099e-06</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666508e-06</v>
+        <v>1.289816639666505e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D181" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D198" t="n">
-        <v>2.301840321336912e-06</v>
+        <v>2.301840321336905e-06</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620881e-05</v>
+        <v>2.767509107620882e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7979,7 +7979,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8008,10 +8008,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C226" t="n">
-        <v>5.522161491500571e-05</v>
+        <v>5.522161491500572e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8075,7 +8075,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D228" t="n">
-        <v>5.308700960874859e-06</v>
+        <v>5.308700960874886e-06</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8424,10 +8424,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>6.598963615398509e-05</v>
+        <v>6.598963615398507e-05</v>
       </c>
       <c r="D239" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D240" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D243" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8712,10 +8712,10 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0002086078173034695</v>
+        <v>0.0002086078173034694</v>
       </c>
       <c r="D248" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8808,10 +8808,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C251" t="n">
-        <v>8.062279496655766e-05</v>
+        <v>8.062279496655767e-05</v>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8939,7 +8939,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9128,10 +9128,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0001726036365800672</v>
+        <v>0.0001726036365800673</v>
       </c>
       <c r="D261" t="n">
-        <v>7.935799382991616e-06</v>
+        <v>7.935799382991588e-06</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9163,7 +9163,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D262" t="n">
-        <v>2.280527714113034e-06</v>
+        <v>2.280527714113048e-06</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9192,10 +9192,10 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C263" t="n">
-        <v>6.449823597324612e-05</v>
+        <v>6.449823597324613e-05</v>
       </c>
       <c r="D263" t="n">
-        <v>1.289964719464938e-06</v>
+        <v>1.289964719464924e-06</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0009141696292534282</v>
+        <v>0.0009141696292534283</v>
       </c>
       <c r="D271" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9576,10 +9576,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C275" t="n">
-        <v>6.709560770963846e-05</v>
+        <v>6.709560770963845e-05</v>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -9608,10 +9608,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C276" t="n">
-        <v>0.0001298000041536001</v>
+        <v>0.0001298000041536002</v>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503159e-05</v>
+        <v>8.507535245503157e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9800,10 +9800,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9864,10 +9864,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>4.640768796898539e-05</v>
+        <v>4.640768796898538e-05</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9896,10 +9896,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C285" t="n">
-        <v>4.338018393197988e-05</v>
+        <v>4.338018393197987e-05</v>
       </c>
       <c r="D285" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>9.498551005356438e-05</v>
+        <v>9.498551005356439e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11115,7 +11115,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D325" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11240,10 +11240,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11368,10 +11368,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C331" t="n">
-        <v>5.522161491500571e-05</v>
+        <v>5.522161491500572e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13543,7 +13543,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D399" t="n">
-        <v>5.308700960874859e-06</v>
+        <v>5.308700960874886e-06</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13683,7 +13683,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D404" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D405" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>6.598963615398509e-05</v>
+        <v>6.598963615398507e-05</v>
       </c>
       <c r="D422" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr"/>
@@ -14215,7 +14215,7 @@
         <v>0.0001123411904081049</v>
       </c>
       <c r="D423" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D429" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14604,10 +14604,10 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="C437" t="n">
-        <v>0.0002086078173034695</v>
+        <v>0.0002086078173034694</v>
       </c>
       <c r="D437" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.276587122712603e-06</v>
+        <v>2.2765871227126e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14856,10 +14856,10 @@
         <v>8.062279496655766e-05</v>
       </c>
       <c r="C446" t="n">
-        <v>8.062279496655766e-05</v>
+        <v>8.062279496655767e-05</v>
       </c>
       <c r="D446" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15055,7 +15055,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D453" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0001726036365800672</v>
+        <v>0.0001726036365800673</v>
       </c>
       <c r="D462" t="n">
-        <v>7.935799382991616e-06</v>
+        <v>7.935799382991588e-06</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15335,7 +15335,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D463" t="n">
-        <v>2.280527714113034e-06</v>
+        <v>2.280527714113048e-06</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582749e-06</v>
+        <v>2.991280417582752e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15388,10 +15388,10 @@
         <v>3.459325613575122e-05</v>
       </c>
       <c r="C465" t="n">
-        <v>3.095186075304056e-05</v>
+        <v>3.095186075304057e-05</v>
       </c>
       <c r="D465" t="n">
-        <v>3.641395382710656e-06</v>
+        <v>3.64139538271065e-06</v>
       </c>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
@@ -15528,10 +15528,10 @@
         <v>6.578820069271105e-05</v>
       </c>
       <c r="C470" t="n">
-        <v>6.449823597324612e-05</v>
+        <v>6.449823597324613e-05</v>
       </c>
       <c r="D470" t="n">
-        <v>1.289964719464938e-06</v>
+        <v>1.289964719464924e-06</v>
       </c>
       <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0009141696292534282</v>
+        <v>0.0009141696292534283</v>
       </c>
       <c r="D547" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17796,10 +17796,10 @@
         <v>4.386457426798799e-05</v>
       </c>
       <c r="C551" t="n">
-        <v>4.210999129726846e-05</v>
+        <v>4.210999129726847e-05</v>
       </c>
       <c r="D551" t="n">
-        <v>1.754582970719526e-06</v>
+        <v>1.75458297071952e-06</v>
       </c>
       <c r="E551" t="inlineStr"/>
       <c r="F551" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961825e-05</v>
+        <v>5.528672749961826e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752826e-06</v>
+        <v>1.316350654752819e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C557" t="n">
-        <v>6.709560770963846e-05</v>
+        <v>6.709560770963845e-05</v>
       </c>
       <c r="D557" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
@@ -17992,10 +17992,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C558" t="n">
-        <v>0.0001298000041536001</v>
+        <v>0.0001298000041536002</v>
       </c>
       <c r="D558" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503159e-05</v>
+        <v>8.507535245503157e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18244,10 +18244,10 @@
         <v>0.0001555597038143239</v>
       </c>
       <c r="C567" t="n">
-        <v>0.0001555597038143239</v>
+        <v>0.000155559703814324</v>
       </c>
       <c r="D567" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="D568" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18468,10 +18468,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>4.640768796898539e-05</v>
+        <v>4.640768796898538e-05</v>
       </c>
       <c r="D575" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr"/>
@@ -18496,10 +18496,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C576" t="n">
-        <v>4.338018393197988e-05</v>
+        <v>4.338018393197987e-05</v>
       </c>
       <c r="D576" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>9.498551005356438e-05</v>
+        <v>9.498551005356439e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D683" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21828,10 +21828,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C695" t="n">
-        <v>3.814343201886828e-05</v>
+        <v>3.814343201886829e-05</v>
       </c>
       <c r="D695" t="n">
-        <v>5.085790935849106e-06</v>
+        <v>5.085790935849099e-06</v>
       </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666508e-06</v>
+        <v>1.289816639666505e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D701" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D703" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22276,10 +22276,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22531,7 +22531,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D720" t="n">
-        <v>2.301840321336912e-06</v>
+        <v>2.301840321336905e-06</v>
       </c>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620881e-05</v>
+        <v>2.767509107620882e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -23287,7 +23287,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D747" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>
@@ -23312,10 +23312,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C748" t="n">
-        <v>5.522161491500571e-05</v>
+        <v>5.522161491500572e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D30" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738257e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D74" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C76" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D76" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C77" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D93" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D161" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C165" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C173" t="n">
-        <v>3.814343201886829e-05</v>
+        <v>3.814343201886828e-05</v>
       </c>
       <c r="D173" t="n">
-        <v>5.085790935849099e-06</v>
+        <v>5.085790935849106e-06</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738257e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D181" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>3.064100992768722e-05</v>
+        <v>3.064100992768721e-05</v>
       </c>
       <c r="D183" t="n">
-        <v>3.953678700346738e-06</v>
+        <v>3.953678700346745e-06</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D191" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D196" t="n">
-        <v>9.093652217404419e-06</v>
+        <v>9.093652217404422e-06</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D197" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218099e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D198" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7307,7 +7307,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D204" t="n">
-        <v>4.367602868959212e-06</v>
+        <v>4.367602868959216e-06</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D209" t="n">
-        <v>4.404238639266429e-06</v>
+        <v>4.404238639266426e-06</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D224" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8008,10 +8008,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C226" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D226" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8075,7 +8075,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D228" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
@@ -8331,7 +8331,7 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8520,10 +8520,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0002766307721372088</v>
+        <v>0.0002766307721372089</v>
       </c>
       <c r="D242" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8712,10 +8712,10 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0002086078173034694</v>
+        <v>0.0002086078173034695</v>
       </c>
       <c r="D248" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8744,10 +8744,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0003025523514765547</v>
+        <v>0.0003025523514765548</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8939,7 +8939,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D255" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -9096,10 +9096,10 @@
         <v>0.0001449275362318841</v>
       </c>
       <c r="C260" t="n">
-        <v>0.0001405357927097057</v>
+        <v>0.0001405357927097058</v>
       </c>
       <c r="D260" t="n">
-        <v>4.391743522178307e-06</v>
+        <v>4.39174352217828e-06</v>
       </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
@@ -9128,10 +9128,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D261" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9163,7 +9163,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D262" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -9291,7 +9291,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9448,10 +9448,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0009141696292534283</v>
+        <v>0.0009141696292534281</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
@@ -9480,10 +9480,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C272" t="n">
-        <v>0.000734172278113636</v>
+        <v>0.0007341722781136361</v>
       </c>
       <c r="D272" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
@@ -9576,10 +9576,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C275" t="n">
-        <v>6.709560770963845e-05</v>
+        <v>6.709560770963846e-05</v>
       </c>
       <c r="D275" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9864,10 +9864,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C284" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D284" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9928,10 +9928,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C286" t="n">
-        <v>6.295184515171395e-05</v>
+        <v>6.295184515171394e-05</v>
       </c>
       <c r="D286" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10187,7 +10187,7 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D317" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C319" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738257e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D325" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11240,10 +11240,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D329" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -11368,10 +11368,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C331" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D331" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
@@ -11435,7 +11435,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13032,10 +13032,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C383" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D383" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13543,7 +13543,7 @@
         <v>0.000169878430747996</v>
       </c>
       <c r="D399" t="n">
-        <v>5.308700960874886e-06</v>
+        <v>5.308700960874859e-06</v>
       </c>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="D413" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002766307721372088</v>
+        <v>0.0002766307721372089</v>
       </c>
       <c r="D428" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14604,10 +14604,10 @@
         <v>0.0002086078173034695</v>
       </c>
       <c r="C437" t="n">
-        <v>0.0002086078173034694</v>
+        <v>0.0002086078173034695</v>
       </c>
       <c r="D437" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0003025523514765547</v>
+        <v>0.0003025523514765548</v>
       </c>
       <c r="D438" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14719,7 +14719,7 @@
         <v>2.427596921807103e-05</v>
       </c>
       <c r="D441" t="n">
-        <v>3.034496152258877e-06</v>
+        <v>3.03449615225888e-06</v>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.2765871227126e-06</v>
+        <v>2.276587122712603e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -15055,7 +15055,7 @@
         <v>0.0001222799176763371</v>
       </c>
       <c r="D453" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
@@ -15276,10 +15276,10 @@
         <v>0.0001449275362318841</v>
       </c>
       <c r="C461" t="n">
-        <v>0.0001405357927097057</v>
+        <v>0.0001405357927097058</v>
       </c>
       <c r="D461" t="n">
-        <v>4.391743522178307e-06</v>
+        <v>4.39174352217828e-06</v>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D462" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15335,7 +15335,7 @@
         <v>0.0001147865616103566</v>
       </c>
       <c r="D463" t="n">
-        <v>2.280527714113048e-06</v>
+        <v>2.280527714113034e-06</v>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582752e-06</v>
+        <v>2.991280417582749e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15388,10 +15388,10 @@
         <v>3.459325613575122e-05</v>
       </c>
       <c r="C465" t="n">
-        <v>3.095186075304057e-05</v>
+        <v>3.095186075304056e-05</v>
       </c>
       <c r="D465" t="n">
-        <v>3.64139538271065e-06</v>
+        <v>3.641395382710656e-06</v>
       </c>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
@@ -15643,7 +15643,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D474" t="n">
-        <v>0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17463,7 +17463,7 @@
         <v>0.0001867176530337884</v>
       </c>
       <c r="D539" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17684,10 +17684,10 @@
         <v>0.0009141696292534282</v>
       </c>
       <c r="C547" t="n">
-        <v>0.0009141696292534283</v>
+        <v>0.0009141696292534281</v>
       </c>
       <c r="D547" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr"/>
@@ -17712,10 +17712,10 @@
         <v>0.0007341722781136361</v>
       </c>
       <c r="C548" t="n">
-        <v>0.000734172278113636</v>
+        <v>0.0007341722781136361</v>
       </c>
       <c r="D548" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         <v>6.709560770963846e-05</v>
       </c>
       <c r="C557" t="n">
-        <v>6.709560770963845e-05</v>
+        <v>6.709560770963846e-05</v>
       </c>
       <c r="D557" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D559" t="n">
-        <v>0</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         <v>3.090456559769982e-05</v>
       </c>
       <c r="C569" t="n">
-        <v>2.869709662643554e-05</v>
+        <v>2.869709662643555e-05</v>
       </c>
       <c r="D569" t="n">
-        <v>2.207468971264276e-06</v>
+        <v>2.207468971264272e-06</v>
       </c>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr"/>
@@ -18356,10 +18356,10 @@
         <v>3.192091676872959e-05</v>
       </c>
       <c r="C571" t="n">
-        <v>3.150090470598316e-05</v>
+        <v>3.150090470598315e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>4.200120627464378e-07</v>
+        <v>4.200120627464445e-07</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18468,10 +18468,10 @@
         <v>4.640768796898539e-05</v>
       </c>
       <c r="C575" t="n">
-        <v>4.640768796898538e-05</v>
+        <v>4.640768796898539e-05</v>
       </c>
       <c r="D575" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr"/>
@@ -18524,10 +18524,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C577" t="n">
-        <v>6.295184515171395e-05</v>
+        <v>6.295184515171394e-05</v>
       </c>
       <c r="D577" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18860,10 +18860,10 @@
         <v>3.872023028148663e-05</v>
       </c>
       <c r="C589" t="n">
-        <v>3.68314385604385e-05</v>
+        <v>3.683143856043851e-05</v>
       </c>
       <c r="D589" t="n">
-        <v>1.88879172104813e-06</v>
+        <v>1.888791721048123e-06</v>
       </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr"/>
@@ -19003,7 +19003,7 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684899</v>
+        <v>0.0008306888183684898</v>
       </c>
       <c r="D683" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C687" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21716,10 +21716,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C691" t="n">
-        <v>5.461827891734432e-05</v>
+        <v>5.461827891734434e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>3.388131789017201e-21</v>
+        <v>0</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21828,10 +21828,10 @@
         <v>4.322922295471739e-05</v>
       </c>
       <c r="C695" t="n">
-        <v>3.814343201886829e-05</v>
+        <v>3.814343201886828e-05</v>
       </c>
       <c r="D695" t="n">
-        <v>5.085790935849099e-06</v>
+        <v>5.085790935849106e-06</v>
       </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>7.138833436738254e-05</v>
+        <v>7.138833436738257e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22055,7 +22055,7 @@
         <v>0.0001183179011167683</v>
       </c>
       <c r="D703" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C705" t="n">
-        <v>3.064100992768722e-05</v>
+        <v>3.064100992768721e-05</v>
       </c>
       <c r="D705" t="n">
-        <v>3.953678700346738e-06</v>
+        <v>3.953678700346745e-06</v>
       </c>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22276,10 +22276,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>3.680270072143241e-05</v>
+        <v>3.68027007214324e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142017e-05</v>
+        <v>8.189553055142015e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22332,10 +22332,10 @@
         <v>5.561865052818271e-05</v>
       </c>
       <c r="C713" t="n">
-        <v>5.561865052818272e-05</v>
+        <v>5.561865052818271e-05</v>
       </c>
       <c r="D713" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>5.690058155312326e-05</v>
+        <v>5.690058155312325e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22475,7 +22475,7 @@
         <v>2.480086968383025e-05</v>
       </c>
       <c r="D718" t="n">
-        <v>9.093652217404419e-06</v>
+        <v>9.093652217404422e-06</v>
       </c>
       <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr"/>
@@ -22503,7 +22503,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D719" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218099e-06</v>
       </c>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr"/>
@@ -22531,7 +22531,7 @@
         <v>3.337668465938518e-05</v>
       </c>
       <c r="D720" t="n">
-        <v>2.301840321336905e-06</v>
+        <v>2.301840321336912e-06</v>
       </c>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -22699,7 +22699,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D726" t="n">
-        <v>4.367602868959212e-06</v>
+        <v>4.367602868959216e-06</v>
       </c>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr"/>
@@ -22839,7 +22839,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D731" t="n">
-        <v>4.404238639266429e-06</v>
+        <v>4.404238639266426e-06</v>
       </c>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D746" t="n">
-        <v>8.43940255781402e-07</v>
+        <v>8.439402557814291e-07</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
@@ -23312,10 +23312,10 @@
         <v>5.522161491500571e-05</v>
       </c>
       <c r="C748" t="n">
-        <v>5.522161491500572e-05</v>
+        <v>5.522161491500571e-05</v>
       </c>
       <c r="D748" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1455,7 +1455,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D37" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>5.461827891734434e-05</v>
+        <v>5.461827891734433e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>-3.388131789017201e-21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D68" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>7.138833436738257e-05</v>
+        <v>7.138833436738255e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142018e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C78" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D105" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D112" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C165" t="n">
-        <v>2.998886128009597e-05</v>
+        <v>2.998886128009596e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027418e-06</v>
+        <v>8.568246080027422e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>5.461827891734434e-05</v>
+        <v>5.461827891734433e-05</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>-3.388131789017201e-21</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666508e-06</v>
+        <v>1.289816639666505e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         <v>4.16096549882235e-05</v>
       </c>
       <c r="C175" t="n">
-        <v>3.677132301284868e-05</v>
+        <v>3.677132301284867e-05</v>
       </c>
       <c r="D175" t="n">
-        <v>4.838331975374819e-06</v>
+        <v>4.838331975374826e-06</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D179" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>7.138833436738257e-05</v>
+        <v>7.138833436738255e-05</v>
       </c>
       <c r="D180" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142018e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6920,10 +6920,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D192" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D197" t="n">
-        <v>3.131201246218099e-06</v>
+        <v>3.131201246218096e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620881e-05</v>
+        <v>2.767509107620882e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7307,7 +7307,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D204" t="n">
-        <v>4.367602868959216e-06</v>
+        <v>4.367602868959212e-06</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D209" t="n">
-        <v>4.404238639266426e-06</v>
+        <v>4.404238639266433e-06</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D225" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
@@ -8139,7 +8139,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D230" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
@@ -8171,7 +8171,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D231" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8424,10 +8424,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C239" t="n">
-        <v>6.598963615398507e-05</v>
+        <v>6.598963615398509e-05</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8744,10 +8744,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0003025523514765548</v>
+        <v>0.0003025523514765547</v>
       </c>
       <c r="D249" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0003117345802716544</v>
+        <v>0.0003117345802716545</v>
       </c>
       <c r="D256" t="n">
-        <v>9.681198145082039e-07</v>
+        <v>9.681198145081497e-07</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9128,10 +9128,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0001726036365800672</v>
+        <v>0.0001726036365800673</v>
       </c>
       <c r="D261" t="n">
-        <v>7.935799382991616e-06</v>
+        <v>7.935799382991588e-06</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9224,10 +9224,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C264" t="n">
-        <v>4.458369214044473e-05</v>
+        <v>4.458369214044474e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.221471017546432e-06</v>
+        <v>1.221471017546425e-06</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9608,10 +9608,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C276" t="n">
-        <v>0.0001298000041536002</v>
+        <v>0.0001298000041536001</v>
       </c>
       <c r="D276" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
@@ -9643,7 +9643,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D277" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503159e-05</v>
+        <v>8.507535245503157e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9832,10 +9832,10 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="C283" t="n">
-        <v>0.0001739054823703317</v>
+        <v>0.0001739054823703318</v>
       </c>
       <c r="D283" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9896,10 +9896,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C285" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
@@ -9928,10 +9928,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C286" t="n">
-        <v>6.295184515171394e-05</v>
+        <v>6.295184515171395e-05</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10152,10 +10152,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C293" t="n">
-        <v>6.822724220135866e-05</v>
+        <v>6.822724220135864e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>5.130361861523299e-05</v>
+        <v>5.130361861523298e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>9.498551005356438e-05</v>
+        <v>9.498551005356439e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10984,10 +10984,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C319" t="n">
-        <v>5.461827891734434e-05</v>
+        <v>5.461827891734433e-05</v>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>-3.388131789017201e-21</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11115,7 +11115,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D323" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11144,10 +11144,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C324" t="n">
-        <v>7.138833436738257e-05</v>
+        <v>7.138833436738255e-05</v>
       </c>
       <c r="D324" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142018e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11339,7 +11339,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D330" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
@@ -11435,7 +11435,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D333" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
@@ -13064,10 +13064,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C384" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D384" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13515,7 +13515,7 @@
         <v>0.001221001221001221</v>
       </c>
       <c r="D398" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
@@ -13683,7 +13683,7 @@
         <v>0.000146911911617794</v>
       </c>
       <c r="D404" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
@@ -13711,7 +13711,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D405" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -14016,10 +14016,10 @@
         <v>1.725661273399967e-05</v>
       </c>
       <c r="C416" t="n">
-        <v>1.380529018719973e-05</v>
+        <v>1.380529018719974e-05</v>
       </c>
       <c r="D416" t="n">
-        <v>3.451322546799936e-06</v>
+        <v>3.451322546799934e-06</v>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
@@ -14184,10 +14184,10 @@
         <v>6.598963615398507e-05</v>
       </c>
       <c r="C422" t="n">
-        <v>6.598963615398507e-05</v>
+        <v>6.598963615398509e-05</v>
       </c>
       <c r="D422" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0003025523514765548</v>
+        <v>0.0003025523514765547</v>
       </c>
       <c r="D438" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
         <v>2.542588354945334e-05</v>
       </c>
       <c r="D440" t="n">
-        <v>4.486920626374119e-06</v>
+        <v>4.486920626374123e-06</v>
       </c>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.276587122712603e-06</v>
+        <v>2.2765871227126e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0003117345802716544</v>
+        <v>0.0003117345802716545</v>
       </c>
       <c r="D454" t="n">
-        <v>9.681198145082039e-07</v>
+        <v>9.681198145081497e-07</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0001726036365800672</v>
+        <v>0.0001726036365800673</v>
       </c>
       <c r="D462" t="n">
-        <v>7.935799382991616e-06</v>
+        <v>7.935799382991588e-06</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15363,7 +15363,7 @@
         <v>2.751977984176126e-05</v>
       </c>
       <c r="D464" t="n">
-        <v>2.991280417582749e-06</v>
+        <v>2.991280417582752e-06</v>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C471" t="n">
-        <v>4.458369214044473e-05</v>
+        <v>4.458369214044474e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.221471017546432e-06</v>
+        <v>1.221471017546425e-06</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -15643,7 +15643,7 @@
         <v>0.001690140845070423</v>
       </c>
       <c r="D474" t="n">
-        <v>-2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961826e-05</v>
+        <v>5.528672749961825e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752819e-06</v>
+        <v>1.316350654752826e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -17992,10 +17992,10 @@
         <v>0.0001298000041536001</v>
       </c>
       <c r="C558" t="n">
-        <v>0.0001298000041536002</v>
+        <v>0.0001298000041536001</v>
       </c>
       <c r="D558" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr"/>
@@ -18023,7 +18023,7 @@
         <v>0.0001384230135851025</v>
       </c>
       <c r="D559" t="n">
-        <v>-5.421010862427522e-20</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503159e-05</v>
+        <v>8.507535245503157e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18272,10 +18272,10 @@
         <v>0.0001739054823703317</v>
       </c>
       <c r="C568" t="n">
-        <v>0.0001739054823703317</v>
+        <v>0.0001739054823703318</v>
       </c>
       <c r="D568" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-5.421010862427522e-20</v>
       </c>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr"/>
@@ -18303,7 +18303,7 @@
         <v>2.869709662643555e-05</v>
       </c>
       <c r="D569" t="n">
-        <v>2.207468971264272e-06</v>
+        <v>2.207468971264269e-06</v>
       </c>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr"/>
@@ -18356,10 +18356,10 @@
         <v>3.192091676872959e-05</v>
       </c>
       <c r="C571" t="n">
-        <v>3.150090470598315e-05</v>
+        <v>3.150090470598316e-05</v>
       </c>
       <c r="D571" t="n">
-        <v>4.200120627464445e-07</v>
+        <v>4.200120627464378e-07</v>
       </c>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr"/>
@@ -18496,10 +18496,10 @@
         <v>4.338018393197987e-05</v>
       </c>
       <c r="C576" t="n">
-        <v>4.338018393197987e-05</v>
+        <v>4.338018393197988e-05</v>
       </c>
       <c r="D576" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr"/>
@@ -18524,10 +18524,10 @@
         <v>6.295184515171394e-05</v>
       </c>
       <c r="C577" t="n">
-        <v>6.295184515171394e-05</v>
+        <v>6.295184515171395e-05</v>
       </c>
       <c r="D577" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915161</v>
+        <v>0.0001237723282915162</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853725e-06</v>
+        <v>1.576717557853698e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18807,7 +18807,7 @@
         <v>2.91604881589805e-05</v>
       </c>
       <c r="D587" t="n">
-        <v>3.72261550965708e-06</v>
+        <v>3.722615509657083e-06</v>
       </c>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr"/>
@@ -18860,10 +18860,10 @@
         <v>3.872023028148663e-05</v>
       </c>
       <c r="C589" t="n">
-        <v>3.683143856043851e-05</v>
+        <v>3.68314385604385e-05</v>
       </c>
       <c r="D589" t="n">
-        <v>1.888791721048123e-06</v>
+        <v>1.88879172104813e-06</v>
       </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr"/>
@@ -18972,10 +18972,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C593" t="n">
-        <v>6.822724220135866e-05</v>
+        <v>6.822724220135864e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>5.130361861523299e-05</v>
+        <v>5.130361861523298e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>9.498551005356438e-05</v>
+        <v>9.498551005356439e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>0</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C687" t="n">
-        <v>2.998886128009597e-05</v>
+        <v>2.998886128009596e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027418e-06</v>
+        <v>8.568246080027422e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21716,10 +21716,10 @@
         <v>5.461827891734434e-05</v>
       </c>
       <c r="C691" t="n">
-        <v>5.461827891734434e-05</v>
+        <v>5.461827891734433e-05</v>
       </c>
       <c r="D691" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>0</v>
+        <v>-3.388131789017201e-21</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666508e-06</v>
+        <v>1.289816639666505e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -21884,10 +21884,10 @@
         <v>4.16096549882235e-05</v>
       </c>
       <c r="C697" t="n">
-        <v>3.677132301284868e-05</v>
+        <v>3.677132301284867e-05</v>
       </c>
       <c r="D697" t="n">
-        <v>4.838331975374819e-06</v>
+        <v>4.838331975374826e-06</v>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D701" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22024,10 +22024,10 @@
         <v>7.138833436738254e-05</v>
       </c>
       <c r="C702" t="n">
-        <v>7.138833436738257e-05</v>
+        <v>7.138833436738255e-05</v>
       </c>
       <c r="D702" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>0</v>
+        <v>6.776263578034403e-21</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142015e-05</v>
+        <v>8.189553055142018e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22360,10 +22360,10 @@
         <v>5.690058155312326e-05</v>
       </c>
       <c r="C714" t="n">
-        <v>5.690058155312325e-05</v>
+        <v>5.690058155312326e-05</v>
       </c>
       <c r="D714" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
@@ -22503,7 +22503,7 @@
         <v>2.426680965819024e-05</v>
       </c>
       <c r="D719" t="n">
-        <v>3.131201246218099e-06</v>
+        <v>3.131201246218096e-06</v>
       </c>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731092e-05</v>
+        <v>5.476250242731093e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620881e-05</v>
+        <v>2.767509107620882e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -22699,7 +22699,7 @@
         <v>2.422034318241015e-05</v>
       </c>
       <c r="D726" t="n">
-        <v>4.367602868959216e-06</v>
+        <v>4.367602868959212e-06</v>
       </c>
       <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr"/>
@@ -22839,7 +22839,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D731" t="n">
-        <v>4.404238639266426e-06</v>
+        <v>4.404238639266433e-06</v>
       </c>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr"/>
@@ -23287,7 +23287,7 @@
         <v>0.0001265628024478735</v>
       </c>
       <c r="D747" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/Kd_jgene_decomposition_CDR3b.xlsx
@@ -1707,7 +1707,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>8.189553055142018e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D73" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D74" t="n">
-        <v>8.439402557814291e-07</v>
+        <v>8.43940255781402e-07</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C82" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5928,10 +5928,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C165" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D165" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D170" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D174" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         <v>4.16096549882235e-05</v>
       </c>
       <c r="C175" t="n">
-        <v>3.677132301284867e-05</v>
+        <v>3.677132301284868e-05</v>
       </c>
       <c r="D175" t="n">
-        <v>4.838331975374826e-06</v>
+        <v>4.838331975374819e-06</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D179" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>3.064100992768721e-05</v>
+        <v>3.064100992768722e-05</v>
       </c>
       <c r="D183" t="n">
-        <v>3.953678700346745e-06</v>
+        <v>3.953678700346738e-06</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D188" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>8.189553055142018e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D190" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7080,10 +7080,10 @@
         <v>2.739801090440834e-05</v>
       </c>
       <c r="C197" t="n">
-        <v>2.426680965819024e-05</v>
+        <v>2.426680965819025e-05</v>
       </c>
       <c r="D197" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218093e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C199" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D199" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C203" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D203" t="n">
         <v>1.006366948225775e-05</v>
@@ -7467,7 +7467,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D209" t="n">
-        <v>4.404238639266433e-06</v>
+        <v>4.404238639266429e-06</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D224" t="n">
-        <v>8.439402557814291e-07</v>
+        <v>8.43940255781402e-07</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
@@ -8331,7 +8331,7 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="D236" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
@@ -8520,10 +8520,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0002766307721372089</v>
+        <v>0.0002766307721372088</v>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8555,7 +8555,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8587,7 +8587,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D244" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8744,10 +8744,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0003025523514765547</v>
+        <v>0.0003025523514765548</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8875,7 +8875,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8968,10 +8968,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0003117345802716545</v>
+        <v>0.0003117345802716544</v>
       </c>
       <c r="D256" t="n">
-        <v>9.681198145081497e-07</v>
+        <v>9.681198145082581e-07</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -9128,10 +9128,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D261" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
@@ -9224,10 +9224,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C264" t="n">
-        <v>4.458369214044474e-05</v>
+        <v>4.458369214044475e-05</v>
       </c>
       <c r="D264" t="n">
-        <v>1.221471017546425e-06</v>
+        <v>1.221471017546419e-06</v>
       </c>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
@@ -9323,7 +9323,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9768,10 +9768,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C281" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D281" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -10120,10 +10120,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D292" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -10152,10 +10152,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C293" t="n">
-        <v>6.822724220135864e-05</v>
+        <v>6.822724220135866e-05</v>
       </c>
       <c r="D293" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -10184,10 +10184,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C294" t="n">
-        <v>5.130361861523298e-05</v>
+        <v>5.130361861523299e-05</v>
       </c>
       <c r="D294" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
@@ -10216,10 +10216,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C295" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D295" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
@@ -10920,10 +10920,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -11019,7 +11019,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D320" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
@@ -11083,7 +11083,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
@@ -11115,7 +11115,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D323" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
@@ -11211,7 +11211,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D326" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
@@ -11240,10 +11240,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C327" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
@@ -11272,10 +11272,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C328" t="n">
-        <v>8.189553055142018e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D328" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
@@ -11307,7 +11307,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D329" t="n">
-        <v>8.439402557814291e-07</v>
+        <v>8.43940255781402e-07</v>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
@@ -13192,10 +13192,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C388" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D388" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
@@ -13711,7 +13711,7 @@
         <v>0.0001651654958268185</v>
       </c>
       <c r="D405" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
         <v>0.0004061646772119051</v>
       </c>
       <c r="D413" t="n">
-        <v>5.421010862427522e-20</v>
+        <v>0</v>
       </c>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
@@ -14352,10 +14352,10 @@
         <v>0.0002766307721372089</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0002766307721372089</v>
+        <v>0.0002766307721372088</v>
       </c>
       <c r="D428" t="n">
-        <v>0</v>
+        <v>5.421010862427522e-20</v>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
         <v>0.0001528498970954214</v>
       </c>
       <c r="D429" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
@@ -14411,7 +14411,7 @@
         <v>0.0001573194698575896</v>
       </c>
       <c r="D430" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>0</v>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
@@ -14632,10 +14632,10 @@
         <v>0.0003025523514765547</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0003025523514765547</v>
+        <v>0.0003025523514765548</v>
       </c>
       <c r="D438" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
@@ -14719,7 +14719,7 @@
         <v>2.427596921807103e-05</v>
       </c>
       <c r="D441" t="n">
-        <v>3.03449615225888e-06</v>
+        <v>3.034496152258877e-06</v>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
         <v>2.845733903390749e-05</v>
       </c>
       <c r="D442" t="n">
-        <v>2.2765871227126e-06</v>
+        <v>2.276587122712603e-06</v>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
@@ -14915,7 +14915,7 @@
         <v>0.0001212219169225796</v>
       </c>
       <c r="D448" t="n">
-        <v>0</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
@@ -15080,10 +15080,10 @@
         <v>0.0003127027000861626</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0003117345802716545</v>
+        <v>0.0003117345802716544</v>
       </c>
       <c r="D454" t="n">
-        <v>9.681198145081497e-07</v>
+        <v>9.681198145082581e-07</v>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
@@ -15304,10 +15304,10 @@
         <v>0.0001805394359630589</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0001726036365800673</v>
+        <v>0.0001726036365800672</v>
       </c>
       <c r="D462" t="n">
-        <v>7.935799382991588e-06</v>
+        <v>7.935799382991616e-06</v>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         <v>4.580516315799117e-05</v>
       </c>
       <c r="C471" t="n">
-        <v>4.458369214044474e-05</v>
+        <v>4.458369214044475e-05</v>
       </c>
       <c r="D471" t="n">
-        <v>1.221471017546425e-06</v>
+        <v>1.221471017546419e-06</v>
       </c>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
@@ -17491,7 +17491,7 @@
         <v>0.0002071181469083418</v>
       </c>
       <c r="D540" t="n">
-        <v>0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr"/>
@@ -17824,10 +17824,10 @@
         <v>5.660307815437108e-05</v>
       </c>
       <c r="C552" t="n">
-        <v>5.528672749961825e-05</v>
+        <v>5.528672749961826e-05</v>
       </c>
       <c r="D552" t="n">
-        <v>1.316350654752826e-06</v>
+        <v>1.316350654752819e-06</v>
       </c>
       <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr"/>
@@ -18216,10 +18216,10 @@
         <v>8.50753524550316e-05</v>
       </c>
       <c r="C566" t="n">
-        <v>8.507535245503157e-05</v>
+        <v>8.507535245503159e-05</v>
       </c>
       <c r="D566" t="n">
-        <v>2.710505431213761e-20</v>
+        <v>1.355252715606881e-20</v>
       </c>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr"/>
@@ -18303,7 +18303,7 @@
         <v>2.869709662643555e-05</v>
       </c>
       <c r="D569" t="n">
-        <v>2.207468971264269e-06</v>
+        <v>2.207468971264272e-06</v>
       </c>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr"/>
@@ -18776,10 +18776,10 @@
         <v>0.0001253490458493699</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0001237723282915162</v>
+        <v>0.0001237723282915161</v>
       </c>
       <c r="D586" t="n">
-        <v>1.576717557853698e-06</v>
+        <v>1.576717557853725e-06</v>
       </c>
       <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr"/>
@@ -18807,7 +18807,7 @@
         <v>2.91604881589805e-05</v>
       </c>
       <c r="D587" t="n">
-        <v>3.722615509657083e-06</v>
+        <v>3.72261550965708e-06</v>
       </c>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr"/>
@@ -18972,10 +18972,10 @@
         <v>6.822724220135866e-05</v>
       </c>
       <c r="C593" t="n">
-        <v>6.822724220135864e-05</v>
+        <v>6.822724220135866e-05</v>
       </c>
       <c r="D593" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         <v>5.130361861523299e-05</v>
       </c>
       <c r="C594" t="n">
-        <v>5.130361861523298e-05</v>
+        <v>5.130361861523299e-05</v>
       </c>
       <c r="D594" t="n">
-        <v>1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr"/>
@@ -19028,10 +19028,10 @@
         <v>9.498551005356438e-05</v>
       </c>
       <c r="C595" t="n">
-        <v>9.498551005356439e-05</v>
+        <v>9.498551005356438e-05</v>
       </c>
       <c r="D595" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr"/>
@@ -21492,10 +21492,10 @@
         <v>0.0008306888183684898</v>
       </c>
       <c r="C683" t="n">
-        <v>0.0008306888183684898</v>
+        <v>0.0008306888183684899</v>
       </c>
       <c r="D683" t="n">
-        <v>0</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         <v>3.855710736012339e-05</v>
       </c>
       <c r="C687" t="n">
-        <v>2.998886128009596e-05</v>
+        <v>2.998886128009597e-05</v>
       </c>
       <c r="D687" t="n">
-        <v>8.568246080027422e-06</v>
+        <v>8.568246080027418e-06</v>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
         <v>2.873232961728537e-05</v>
       </c>
       <c r="D692" t="n">
-        <v>-3.388131789017201e-21</v>
+        <v>3.388131789017201e-21</v>
       </c>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr"/>
@@ -21803,7 +21803,7 @@
         <v>0.0001421700644773554</v>
       </c>
       <c r="D694" t="n">
-        <v>0</v>
+        <v>-2.710505431213761e-20</v>
       </c>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr"/>
@@ -21859,7 +21859,7 @@
         <v>2.70861494329966e-05</v>
       </c>
       <c r="D696" t="n">
-        <v>1.289816639666505e-06</v>
+        <v>1.289816639666508e-06</v>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr"/>
@@ -21884,10 +21884,10 @@
         <v>4.16096549882235e-05</v>
       </c>
       <c r="C697" t="n">
-        <v>3.677132301284867e-05</v>
+        <v>3.677132301284868e-05</v>
       </c>
       <c r="D697" t="n">
-        <v>4.838331975374826e-06</v>
+        <v>4.838331975374819e-06</v>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
         <v>0.0001069187390168411</v>
       </c>
       <c r="D701" t="n">
-        <v>-1.355252715606881e-20</v>
+        <v>0</v>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         <v>3.459468862803396e-05</v>
       </c>
       <c r="C705" t="n">
-        <v>3.064100992768721e-05</v>
+        <v>3.064100992768722e-05</v>
       </c>
       <c r="D705" t="n">
-        <v>3.953678700346745e-06</v>
+        <v>3.953678700346738e-06</v>
       </c>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
         <v>5.042128030135118e-05</v>
       </c>
       <c r="D710" t="n">
-        <v>6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr"/>
@@ -22276,10 +22276,10 @@
         <v>3.68027007214324e-05</v>
       </c>
       <c r="C711" t="n">
-        <v>3.68027007214324e-05</v>
+        <v>3.680270072143241e-05</v>
       </c>
       <c r="D711" t="n">
-        <v>0</v>
+        <v>-6.776263578034403e-21</v>
       </c>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr"/>
@@ -22304,10 +22304,10 @@
         <v>8.189553055142015e-05</v>
       </c>
       <c r="C712" t="n">
-        <v>8.189553055142018e-05</v>
+        <v>8.189553055142017e-05</v>
       </c>
       <c r="D712" t="n">
-        <v>-2.710505431213761e-20</v>
+        <v>-1.355252715606881e-20</v>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
@@ -22500,10 +22500,10 @@
         <v>2.739801090440834e-05</v>
       </c>
       <c r="C719" t="n">
-        <v>2.426680965819024e-05</v>
+        <v>2.426680965819025e-05</v>
       </c>
       <c r="D719" t="n">
-        <v>3.131201246218096e-06</v>
+        <v>3.131201246218093e-06</v>
       </c>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr"/>
@@ -22556,10 +22556,10 @@
         <v>5.476250242731092e-05</v>
       </c>
       <c r="C721" t="n">
-        <v>5.476250242731093e-05</v>
+        <v>5.476250242731092e-05</v>
       </c>
       <c r="D721" t="n">
-        <v>-6.776263578034403e-21</v>
+        <v>0</v>
       </c>
       <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr"/>
@@ -22668,7 +22668,7 @@
         <v>3.773876055846656e-05</v>
       </c>
       <c r="C725" t="n">
-        <v>2.767509107620882e-05</v>
+        <v>2.767509107620881e-05</v>
       </c>
       <c r="D725" t="n">
         <v>1.006366948225775e-05</v>
@@ -22839,7 +22839,7 @@
         <v>2.013366235093225e-05</v>
       </c>
       <c r="D731" t="n">
-        <v>4.404238639266433e-06</v>
+        <v>4.404238639266429e-06</v>
       </c>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
         <v>0.0001544410668079985</v>
       </c>
       <c r="D746" t="n">
-        <v>8.439402557814291e-07</v>
+        <v>8.43940255781402e-07</v>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
